--- a/http-rpc性能对比.xlsx
+++ b/http-rpc性能对比.xlsx
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>cloud-http</t>
   </si>
   <si>
-    <t>cloud-nonacos-http2</t>
+    <t>cloud-nonacos-http2-h2(https)</t>
+  </si>
+  <si>
+    <t>cloud-nonacos-http2-h2c(http)</t>
   </si>
   <si>
     <t>cloud-grpc</t>
@@ -88,6 +91,27 @@
   </si>
   <si>
     <t>========== Benchmark 入参 ==========
+测试类型       ：cloud-http2
+测试说明       ：Cloud HTTP2 本地性能测试
+并发线程数     ：100
+请求总数       ：10000
+====================================
+========== Benchmark 测试结果 ==========
+测试类型       ：cloud-http2
+并发线程数     ：100
+请求总数       ：10000
+总耗时(ms)     ：3180
+吞吐量(QPS)    ：3144.65
+平均延迟(ms)   ：31
+P95 延迟(ms)   ：62
+P99 延迟(ms)   ：536
+CPU 使用率(%)  ：26.47
+已用堆内存(MB) ：53
+最大堆内存(MB) ：4096
+========================================</t>
+  </si>
+  <si>
+    <t>========== Benchmark 入参 ==========
 测试类型       ：cloud-grpc
 测试说明       ：Cloud gRPC 本地性能测试
 并发线程数     ：100
@@ -196,6 +220,28 @@
   </si>
   <si>
     <t xml:space="preserve">========== Benchmark 入参 ==========
+测试类型       ：cloud-http2
+测试说明       ：Cloud HTTP2 本地性能测试
+并发线程数     ：100
+请求总数       ：10000
+====================================
+========== Benchmark 测试结果 ==========
+测试类型       ：cloud-http2
+并发线程数     ：100
+请求总数       ：10000
+总耗时(ms)     ：2620
+吞吐量(QPS)    ：3816.79
+平均延迟(ms)   ：25
+P95 延迟(ms)   ：54
+P99 延迟(ms)   ：185
+CPU 使用率(%)  ：28.24
+已用堆内存(MB) ：160
+最大堆内存(MB) ：4096
+========================================
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">========== Benchmark 入参 ==========
 测试类型       ：cloud-grpc
 测试说明       ：Cloud gRPC 本地性能测试
 并发线程数     ：100
@@ -305,6 +351,27 @@
 </t>
   </si>
   <si>
+    <t>========== Benchmark 入参 ==========
+测试类型       ：cloud-http2
+测试说明       ：Cloud HTTP2 本地性能测试
+并发线程数     ：100
+请求总数       ：10000
+====================================
+========== Benchmark 测试结果 ==========
+测试类型       ：cloud-http2
+并发线程数     ：100
+请求总数       ：10000
+总耗时(ms)     ：1441
+吞吐量(QPS)    ：6939.63
+平均延迟(ms)   ：13
+P95 延迟(ms)   ：21
+P99 延迟(ms)   ：55
+CPU 使用率(%)  ：35.95
+已用堆内存(MB) ：400
+最大堆内存(MB) ：4096
+========================================</t>
+  </si>
+  <si>
     <t xml:space="preserve">========== Benchmark 入参 ==========
 测试类型       ：cloud-grpc
 测试说明       ：Cloud gRPC 本地性能测试
@@ -366,6 +433,49 @@
 P99 延迟(ms)   ：26
 CPU 使用率(%)  ：26.74
 已用堆内存(MB) ：113
+最大堆内存(MB) ：4096
+========================================
+</t>
+  </si>
+  <si>
+    <t>========== Benchmark 入参 ==========
+测试类型       ：cloud-http2
+测试说明       ：Cloud HTTP2 本地性能测试
+并发线程数     ：100
+请求总数       ：10000
+====================================
+========== Benchmark 测试结果 ==========
+测试类型       ：cloud-http2
+并发线程数     ：100
+请求总数       ：10000
+总耗时(ms)     ：1610
+吞吐量(QPS)    ：6211.18
+平均延迟(ms)   ：15
+P95 延迟(ms)   ：23
+P99 延迟(ms)   ：28
+CPU 使用率(%)  ：31.90
+已用堆内存(MB) ：521
+最大堆内存(MB) ：4096
+========================================</t>
+  </si>
+  <si>
+    <t xml:space="preserve">========== Benchmark 入参 ==========
+测试类型       ：cloud-http2
+测试说明       ：Cloud HTTP2 本地性能测试
+并发线程数     ：100
+请求总数       ：10000
+====================================
+========== Benchmark 测试结果 ==========
+测试类型       ：cloud-http2
+并发线程数     ：100
+请求总数       ：10000
+总耗时(ms)     ：1737
+吞吐量(QPS)    ：5757.05
+平均延迟(ms)   ：16
+P95 延迟(ms)   ：31
+P99 延迟(ms)   ：43
+CPU 使用率(%)  ：31.52
+已用堆内存(MB) ：211
 最大堆内存(MB) ：4096
 ========================================
 </t>
@@ -990,7 +1100,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1003,11 +1113,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1534,13 +1650,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="E4:I7"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="6"/>
+  <dimension ref="E4:J9"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
-    <col min="5" max="9" width="60.7403846153846" customWidth="1"/>
+    <col min="5" max="10" width="60.7403846153846" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="5:9">
+    <row r="4" spans="5:10">
       <c r="E4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1556,56 +1672,79 @@
       <c r="I4" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="J4" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" ht="387" spans="5:9">
-      <c r="E5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="5" t="s">
+    <row r="5" ht="387" spans="5:10">
+      <c r="E5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="H5" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="I5" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="6" ht="387" spans="5:9">
-      <c r="E6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="5" t="s">
+    <row r="6" ht="387" spans="5:10">
+      <c r="E6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="G6" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="H6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="7" ht="387" spans="5:9">
-      <c r="E7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>17</v>
+    <row r="7" ht="387" spans="5:10">
+      <c r="E7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" ht="353" spans="5:10">
+      <c r="F8" s="2"/>
+      <c r="G8" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" ht="387" spans="5:10">
+      <c r="G9" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
